--- a/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_B_USD_2026-10_mtd.xlsx
+++ b/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_B_USD_2026-10_mtd.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -476,31 +476,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIRE-20261008-B01</t>
+          <t>CHQ-000417</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>cheque</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wire to Lakeside Legal LLP - legal fees</t>
+          <t>CHEQUE 000417 presented, payee not shown</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lakeside Legal LLP</t>
+          <t>Unknown payee</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-12400</v>
+        <v>-2150</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,31 +511,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BF-HB-B-USD-10</t>
+          <t>WIRE-20261008-B01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bank_fee</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Account maintenance fee</t>
+          <t>Wire to Lakeside Legal LLP - legal fees</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Harbour Bank (synthetic)</t>
+          <t>Lakeside Legal LLP</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-37.96</v>
+        <v>-12400</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -551,28 +551,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>BF-HB-B-USD-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bank_fee</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Account maintenance fee</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Harbour Bank (synthetic)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-37.96</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>IN-HB-B-USD-10</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Credit interest</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Harbour Bank (synthetic)</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>65.47</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -649,13 +684,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>704314.35</v>
+        <v>706464.35</v>
       </c>
       <c r="E2" t="n">
         <v>-23914.35</v>
       </c>
       <c r="F2" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
     </row>
     <row r="3">
@@ -675,13 +710,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
     </row>
     <row r="4">
@@ -701,13 +736,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
     </row>
     <row r="5">
@@ -727,10 +762,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>680400</v>
+        <v>682550</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-2150</v>
       </c>
       <c r="F5" t="n">
         <v>680400</v>
